--- a/artfynd/A 69915-2021 artfynd.xlsx
+++ b/artfynd/A 69915-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69915-2021 artfynd.xlsx
+++ b/artfynd/A 69915-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>80554805</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588741.2010684104</v>
+        <v>588741</v>
       </c>
       <c r="R2" t="n">
-        <v>7174407.844504614</v>
+        <v>7174408</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
